--- a/docs/importantes/Maestro de documentos fase 1.xlsx
+++ b/docs/importantes/Maestro de documentos fase 1.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="553S2Hcg9xgk+CoRtfkzt9LxmajL58CZAqKmbfQKjzc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="S6t7t/FrldKehca4Fip3fG06E/LeBUXiHfxuGF1fXXg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="254">
   <si>
     <t>Fase</t>
   </si>
@@ -602,15 +602,198 @@
   </si>
   <si>
     <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/plan%20de%20calidad%20Print(Null)2.pdf</t>
+  </si>
+  <si>
+    <t>Diseño</t>
+  </si>
+  <si>
+    <t>Script definicion de procesos (Diseño)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diligenciar documento </t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/script/Script%20definici%C3%B3n%20de%20procesos%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>UML despliegue</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde al despliegue del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/UML%20Despliegue.drawio%20(1).pdf</t>
+  </si>
+  <si>
+    <t>UML desarrollo</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde al desarrollo del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>16/septiempre/2025</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/vista%20desarrollo.jpg</t>
+  </si>
+  <si>
+    <t>Modelo de datos Entidad relación</t>
+  </si>
+  <si>
+    <t>Diagrama de modelo de datos del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/modelo%20datos.jpg</t>
+  </si>
+  <si>
+    <t>UML de casos de uso (Vista de contexto)</t>
+  </si>
+  <si>
+    <t>Diagrama de modelo de casos de uso del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/VISTA%20CONTEXTO%20RESUMIDA.pdf</t>
+  </si>
+  <si>
+    <t>UML contexto</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde al contexto del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/VISTA%20CONTEXTO%202.pdf</t>
+  </si>
+  <si>
+    <t>UML funcional</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde al funciones del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/vista%20funcional.jpg</t>
+  </si>
+  <si>
+    <t>UML información</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde a la información del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/vista%20Informacion.drawio.png</t>
+  </si>
+  <si>
+    <t>UML concurrencia</t>
+  </si>
+  <si>
+    <t>Diagrama UML que corresponde al concurrencia del proyecto DASHKPI'S</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/vista%20concurrencia.jpg</t>
+  </si>
+  <si>
+    <t>SDS</t>
+  </si>
+  <si>
+    <t>DOCUMENTO SDS DE ESPECIFICACION DE DISEÑO DE SOFTWARE</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/assets/nicolas.jpg</t>
+  </si>
+  <si>
+    <t>Interfaz usuario</t>
+  </si>
+  <si>
+    <t>Mokup de la interfaz del proyecto</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/interfaz%203.jpg</t>
+  </si>
+  <si>
+    <t>Modelo de clases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo de clases del proyecto </t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/vistas/MODELO%20CLASES.pdf</t>
+  </si>
+  <si>
+    <t>Plan de Seguimiento de Riesgos - Fase de Diseño (SDS)</t>
+  </si>
+  <si>
+    <t>Plantilla de seguimiento de riesgos de la fase 5 de Diseño</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/Plan_Seguimiento_Riesgos_Fase_Dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/santiago/BitacoraTiempodef_Santiago_Herrada%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/esteban/BitacoraTiempo%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>BitacoraTiempo Nicolás Cubillos</t>
+  </si>
+  <si>
+    <t>Registro de tiempo de trabajo realizado por Nicolás Cubillos en el proyecto.</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/nicolas/BitacoraTiempo[5],%20Nicolas%20Cubillos%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/kerlon/BitacoraTiempoKerlon%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/matias/BitacoraMatias%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/bitacoras/leidy/BitacoraTiempo%20Leidy%20Giraldo%20fase%20dise%C3%B1o.pdf</t>
+  </si>
+  <si>
+    <t>Documento que detalla el control de asignaciones en la fase de Diseño del proyecto.</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/control/dt_ptl_controlAsignaciones_definitivo%20fase%20dise%C3%B1o.xlsx</t>
+  </si>
+  <si>
+    <t>logDefectos fase 5</t>
+  </si>
+  <si>
+    <t>Documento donde se registran los defectos encontrados en la fase 5 del proyecto.</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/log%20defectos/logDefectos%20fase%205.pdf</t>
+  </si>
+  <si>
+    <t>Informe Final fase 5</t>
+  </si>
+  <si>
+    <t>Informe que resume los resultados y actividades realizadas durante la fase 5 del proyecto.</t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/informes/Informe%20Final%20fase%205.pdf</t>
+  </si>
+  <si>
+    <t>Checklist fase 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza un checklist con los comentarios de los integrantes </t>
+  </si>
+  <si>
+    <t>https://leidygbeta1.github.io/Print-Null-/docs/importantes/CheckList.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="d/mmmm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="168" formatCode="d/mmmmyyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -676,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -706,6 +889,18 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -3901,7 +4096,7 @@
         <v>45907.0</v>
       </c>
       <c r="F17" s="5">
-        <v>45908.0</v>
+        <v>45914.0</v>
       </c>
       <c r="G17" s="4">
         <v>2.0</v>
@@ -3982,6 +4177,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="49.29"/>
+    <col customWidth="1" min="4" max="4" width="79.86"/>
+    <col customWidth="1" min="5" max="5" width="20.43"/>
+    <col customWidth="1" min="6" max="6" width="20.14"/>
+    <col customWidth="1" min="8" max="8" width="111.29"/>
+  </cols>
   <sheetData>
     <row r="6">
       <c r="B6" s="1" t="s">
@@ -4007,285 +4209,691 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="B7" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="13">
+        <v>45915.0</v>
+      </c>
+      <c r="F7" s="13">
+        <v>45915.0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="B8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="13">
+        <v>45915.0</v>
+      </c>
+      <c r="F8" s="13">
+        <v>45915.0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
+      <c r="B9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" s="13">
+        <v>45916.0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="B10" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="13">
+        <v>45916.0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
+      <c r="B11" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="13">
+        <v>45916.0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="B12" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
+      <c r="B13" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F13" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
+      <c r="B14" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F14" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
+      <c r="B15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E15" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F15" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="B16" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="B17" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="B18" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="B19" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E19" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="F19" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="B20" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="B21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="13">
+        <v>45916.0</v>
+      </c>
+      <c r="F21" s="16">
+        <v>45916.0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="B22" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="13">
+        <v>45916.0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>45916.0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="B23" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F23" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="B24" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F24" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="B25" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="F25" s="7">
+        <v>45916.0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="B26" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="F26" s="15">
+        <v>45916.0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="B27" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="B28" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="F28" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="B29" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="F29" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="B30" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E30" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>45917.0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
     </row>
     <row r="32">
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
     </row>
     <row r="33">
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34">
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35">
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36">
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
     </row>
     <row r="37">
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="H7"/>
+    <hyperlink r:id="rId2" ref="H8"/>
+    <hyperlink r:id="rId3" ref="H9"/>
+    <hyperlink r:id="rId4" ref="H10"/>
+    <hyperlink r:id="rId5" ref="H11"/>
+    <hyperlink r:id="rId6" ref="H12"/>
+    <hyperlink r:id="rId7" ref="H13"/>
+    <hyperlink r:id="rId8" ref="H14"/>
+    <hyperlink r:id="rId9" ref="H15"/>
+    <hyperlink r:id="rId10" ref="H16"/>
+    <hyperlink r:id="rId11" ref="H17"/>
+    <hyperlink r:id="rId12" ref="H18"/>
+    <hyperlink r:id="rId13" ref="H19"/>
+    <hyperlink r:id="rId14" ref="H20"/>
+    <hyperlink r:id="rId15" ref="H21"/>
+    <hyperlink r:id="rId16" ref="H23"/>
+    <hyperlink r:id="rId17" ref="H24"/>
+    <hyperlink r:id="rId18" ref="H25"/>
+    <hyperlink r:id="rId19" ref="H26"/>
+    <hyperlink r:id="rId20" ref="H27"/>
+    <hyperlink r:id="rId21" ref="H28"/>
+    <hyperlink r:id="rId22" ref="H29"/>
+    <hyperlink r:id="rId23" ref="H30"/>
+  </hyperlinks>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>